--- a/data/daily/2026-10/2026-10-04.xlsx
+++ b/data/daily/2026-10/2026-10-04.xlsx
@@ -1220,14 +1220,64 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1317,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,85 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="381000" cy="457200"/>
+    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1475,27 +1475,77 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,154 +1553,104 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,33 +2596,29 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16211</v>
+        <v>16213</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>선물하기 좋은 포장과 구성 — 고급스러운 포장과 브랜드 인지도 덕에 선물용으로 만족도가 매우 높음</t>
+          <t>우수한 섭취 및 휴대성 — 액상과 정제가 함께 있어 물 없이도 간편하게 섭취 가능하며 여행 시 휴대하기 용이함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 꾸준히 섭취 시 아침 피로가 풀리고 기력이 회복되는 느낌을 받음</t>
+          <t>빠른 피로 회복 효과 — 복용 후 기력이 생기고 피로가 풀리며 정신이 드는 효과가 있음</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>간편한 액상 정제 복용 — 액상과 정제를 함께 30초 만에 번거롭지 않게 섭취 가능함</t>
+          <t>선물용으로 높은 만족도 — 패키지가 이쁘고 유명하여 선물용으로 높은 만족도를 얻음</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>짧은 유통기한에 대한 아쉬움 — 수령 후 확인 시 유통기한이 10개월 미만으로 짧게 남아 아쉬움</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>생각보다 작은 케이스 크기 — 손바닥 정도의 매우 작은 크기라 선물용 볼륨감으로 다소 미흡함</t>
-        </is>
-      </c>
+          <t>짧은 유통기한 배송 — 유통기한이 10개월 미만으로 남은 제품이 배송되어 아쉬움</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
@@ -2663,21 +2659,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15526</v>
+        <v>15529</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>깔끔하고 예쁜 선물 패키지 — 패키지 박스가 깔끔하고 예뻐서 지인 선물용으로 매우 적합함</t>
+          <t>맛있는 음료 제형 — 주스처럼 거부감 없이 맛있게 즐길 수 있음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 올인원 영양 케어 — 다양한 비타민과 미네랄을 한 번에 간편하게 챙길 수 있음</t>
+          <t>피로 회복 및 활력 증진 — 섭취 후 피로 해소에 도움이 되고 개운함과 힘이 느껴짐</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>실용적이고 우수한 효과 — 실용적인 선물 구성이며 섭취 후 피로 개선 등 효과에 만족함</t>
+          <t>간편한 섭취와 깔끔한 포장 — 포장이 깔끔하며 간편하게 챙겨 먹기 좋아 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2726,18 +2722,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 포장이 고급스럽고 화려하여 주는 사람과 받는 사람 모두 만족함</t>
+          <t>체감 높은 피로 회복 — 힘들 때 반짝하는 효과를 주어 건강 관리에 도움 됨</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 체감 — 피곤하고 힘들 때 섭취하면 빠르게 기운이 나는 효과를 체감함</t>
+          <t>고급스러운 기프트 포장 — 포장이 고급스럽고 아름다워 선물하기에 마음에 듦</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>발송자 정보 확인 불편 — 보낸 사람 정보 확인이 어렵고 카톡 고객문의 답변도 명확하지 않음</t>
+          <t>보낸 사람 확인 불가 — 선물 보낸 사람의 정보 확인이 불명확하고 문의 답변이 미흡함</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2785,16 +2781,20 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>새콤달콤한 맛있는 구미 — 과일향이 풍부하고 새콤달콤하여 간식처럼 맛있게 먹을 수 있음</t>
+          <t>맛있는 과일 향과 식감 — 새콤달콤한 과일 향과 탱글하고 쫄깃한 식감으로 섭취가 즐거움</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>거부감 없는 간편한 섭취 — 알약을 못 먹거나 목넘김이 어려운 사람도 매일 쉽게 챙겨 먹음</t>
+          <t>편리한 구미 제형 — 씹어먹는 젤리 타입으로 물 없이 간식처럼 매일 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>하루 섭취량 제한의 아쉬움 — 젤리가 너무 맛있어 하루 2개 제한 이상으로 더 먹고 싶어 참기 힘듦</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -2840,20 +2840,20 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>알찬 수량 증정 구성 — 7입에 2입을 추가 증정하는 단독 구성이라 알차고 유용함</t>
+          <t>깔끔하고 알찬 포장 구성 — 포장이 깔끔하고 증정 구성이 포함되어 생일 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>피로 해소 및 기력 회복 — 지치고 피곤할 때 복용하면 아침 컨디션과 기력 회복에 도움 됨</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>외관상 아쉬운 소포장 — 소포장 위주 구성이라 외관상 아주 풍성해 보이지는 않음</t>
-        </is>
-      </c>
+          <t>아침 피로 개선 효과 — 복용 후 피로 해소 및 다음 날 아침 기력 회복에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>간편한 올인원 제형 — 알약과 음료가 함께 있어 여러 영양제를 간편하게 하나로 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>고급스러운 명절 선물 포장 — 고급 박스와 종이가방이 포함되어 명절 선물용으로 격식 있음</t>
+          <t>고급스러운 명절 포장 — 고급 박스와 종이가방 구성으로 명절 선물에 제격임</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>빠른 활력 충전 효과 — 피로감이 심할 때 섭취하면 빠르게 기운이 나고 활력이 생김</t>
+          <t>활력 충전 효과 — 복용 시 피로가 가시고 기운을 차리는 데 도움이 됨</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -2954,18 +2954,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>휴대와 복용의 편리함 — 외출 시 들고 다니며 간편하게 섭취하기 좋은 용기 형태임</t>
+          <t>우수한 휴대성 및 편의성 — 간편하게 들고 다니며 섭취하기에 유용함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>아침 활력 충전 효과 — 아침 복용 시 하루 활력이 생겨 직장 내 에너지 충전에 유용함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>빠른 배송과 가격 만족 — 배송이 빠르고 부담 없는 가격대에 구매가 가능함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>하루 활력 충전 — 아침 복용 시 일상과 사무실에서의 활력을 높여줌</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>다소 높은 당 함유량 — 당 함유량이 4g 포함되어 있어 액상과당 섭취에 부담을 느낌</t>
+          <t>높은 당 함유량 — 당 함유량이 4g으로 다소 높게 느껴져 아쉬움</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -3009,22 +3013,26 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>상큼달콤한 맛과 섞는 재미 — 뚜껑을 눌러 분말을 섞는 재미가 있고 쓴 맛 없이 상큼하게 맛있음</t>
+          <t>상큼하고 달콤한 맛 — 쓴맛 없이 오렌지빛의 달달하고 상큼한 맛으로 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>감기 예방 및 컨디션 회복 — 감기 기운이 있을 때 섭취하면 몸이 가벼워지고 기운이 남</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>재미있는 용기 메커니즘 — 뚜껑을 눌러 가루를 섞어 마시는 간편하고 독특한 재미가 있음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>고급스러운 선물 구성 — 포장과 봉투 구성이 고급스러워 선물용으로 적합함</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>개봉 시 센 악력 필요 — 손 힘이 약한 사람은 뚜껑을 눌러서 열기가 다소 뻑뻑하고 힘듦</t>
+          <t>뚜껑 개봉의 어려움 — 손 힘이 약한 소비자의 경우 뚜껑을 열기 어려울 수 있음</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -3072,18 +3080,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>성별 맞춤형 제품 선택 — 남성용과 여성용이 구분되어 상황에 맞는 선물이 가능함</t>
+          <t>성별 맞춤 선택 가능 — 남성과 여성에 맞춘 영양소 선택이 가능하여 유용함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>쓴맛 없이 편한 복용 — 비타민 특유의 쓴맛이 없고 찐득하게 영양감이 느껴짐</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>부담 없는 맛과 간편성 — 비타민 특유의 쓴맛이 없고 휴대하며 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>지속적인 피로 완화 — 꾸준히 복용 시 피로감이 줄고 활력 유지 효과를 봄</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>삼키기 부담스러운 알약 크기 — 기존 제품에 비해 정제 알약 크기가 커서 삼키기가 다소 힘들음</t>
+          <t>큰 알약 크기 — 기존 제품 대비 알약 크기가 다소 커서 삼키기 힘듦</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3127,27 +3139,23 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>강력한 정신 확 깨는 효과 — 고함량 비타민 복용 시 나른한 컨디션이 개운해지고 정신이 듦</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>선물용으로 훌륭한 브랜드 — 피로를 호소하는 지인에게 선물하기에 기분 좋은 아이템임</t>
-        </is>
-      </c>
+          <t>즉각적인 활력 제공 — 섭취 시 개운해지고 정신이 확 드는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>호불호 갈리는 강한 신맛 — 분말 특유의 신맛이 매우 강하여 섭취 시 강한 자극이 느껴짐</t>
+          <t>강한 신맛으로 인한 거부감 — 분말 특유의 신맛이 매우 강해 섭취 시 맛에 대한 호불호가 갈림</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>캡슐 제형의 부재 — 가루를 직접 삼키기보다 캡슐 형태 제형을 선호하는 수요가 있음</t>
+          <t>제형의 아쉬움 — 분말 형태로 인해 맛이 떨어져 캡슐 제형을 선호하는 의견이 있음</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -3190,16 +3198,16 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>뛰어난 효소 맛과 풍미 — 효소 제품 중 최고 수준으로 맛있으며 골라 먹는 재미가 있음</t>
+          <t>부담 없는 맛있는 풍미 — 효소 특유의 맛에 대한 부담 없이 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>귀여운 굿즈 및 알찬 포장 — 콜라보 포토카드 퀄리티가 훌륭하고 패키지 포장이 예쁨</t>
+          <t>우수한 굿즈 기획 패키지 — 콜라보 굿즈 및 포토카드 포장 퀄리티가 우수함</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -3218,58 +3226,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인키위효소+고단백질바 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>33,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260923111828_e9badd52c1a54899b5226c1eae768639.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>1685</v>
+        <v>60</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>구수하고 거부감 없는 맛 — 구수한 고구마 맛이 나 부담 없이 온 가족이 먹기 좋음</t>
+          <t>부드럽고 촉촉한 식감 — 닭가슴살임에도 퍽퍽하지 않고 매우 부드러움</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>속이 편안해지는 소화 개선 — 식사나 밀가루 섭취 후 복용 시 속이 편해지고 소화에 도움 됨</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>푸짐하고 알찬 증정 사은품 — 파로 곡물바와 차 등 다양한 사은품 구성이 함께 제공됨</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>다양한 맛과 가성비 — 다양한 종류 구성으로 질리지 않으며 세일 가격으로 구매하기 좋음</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>특정 구성의 부재 — 선호하는 파우치형 그릴 제품이 구성에 포함되어 있지 않아 아쉬움</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3277,58 +3285,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인키위효소+고단백질바 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928091559_44d67bbfbab644e3bc688b7716d83f5d.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260923111828_e9badd52c1a54899b5226c1eae768639.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>753</v>
+        <v>1686</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>고급스럽고 예쁜 패키징 — 플리츠백과 오간자 포장 디자인이 화려하여 개봉 시 감동을 줌</t>
+          <t>속 편한 소화 촉진 — 식후나 밀가루 섭취 후 복용 시 속이 편안해지고 소화에 도움을 줌</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>맛있고 섭취 편한 앰플 — 맛이 매우 우수하며 꾸준히 마실 시 피로감이 개선되는 느낌임</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>부담스러운 높은 가격대 — 제품 단가가 높은 편이라 주로 세일 기간이나 선물용으로만 구매함</t>
-        </is>
-      </c>
+          <t>구수한 고구마 맛 — 거부감 없는 구수한 고구마 맛으로 맛있게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>풍성한 사은품 증정 — 함께 증정되는 곡물바 및 사은품의 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3336,49 +3344,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>33,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928091559_44d67bbfbab644e3bc688b7716d83f5d.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>60</v>
+        <v>753</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 식감 — 퍽퍽함과 잡내가 전혀 없고 극상의 부드러움을 느낄 수 있음</t>
+          <t>고급스러운 화려한 포장 — 개봉 시 기분이 좋아질 정도로 포장 패키지가 매우 예쁘고 고급스러움</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>다양한 맛과 가성비 할인 — 소스 및 제품 종류가 다채로워 질리지 않으며 할인가가 매우 저렴함</t>
+          <t>피로 회복 및 우수한 맛 — 맛이 좋고 섭취 시 피로감이 덜함</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>선호 품목 구성 제외 아쉬움 — 개인적으로 선호하는 파우치형 그릴 제품이 빠져있어 아쉬움</t>
+          <t>부담스러운 가격 — 가격대가 높아 할인 시에만 구매하게 됨</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -3426,23 +3434,23 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>우수한 포만감과 한 달 식단 — 한 개만 먹어도 포만감이 높아 다이어트 식단으로 매우 든든함</t>
+          <t>높은 포만감과 맛 — 한 개만 먹어도 속이 든든하며 다양한 소스 맛이 훌륭함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>실용적인 보냉백 사은품 — 증정품으로 오는 보냉 도시락 가방이 예쁘고 들고 다니기 좋음</t>
+          <t>알찬 식단 패키지 — 30팩의 풍성한 수량으로 한 달 식단 관리에 유용함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>제품 터짐 및 소스 누출 — 포장이 헐렁하거나 봉지가 터져서 주변에 소스가 묻어 배송됨</t>
+          <t>구성품 오배송 — 주문한 구성과 다르게 제품이 중복되거나 누락되어 배송됨</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>구성품 오배송 발생 — 안내된 옵션과 다르게 제품이 누락되거나 중복되어 잘못 전달됨</t>
+          <t>포장 파손 및 진공 불량 — 배송 과정에서 제품이 터져 소스가 묻거나 진공 포장이 헐렁함</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -3489,18 +3497,18 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>쫄깃하고 부드러운 식감 — 닭가슴살과 볼 제형 모두 촉촉하고 부드러워 먹기 수월함</t>
+          <t>부드럽고 쫄깃한 맛 — 퍽퍽하지 않고 촉촉하여 맛있게 단백질 충전이 가능함</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>간 편한 데우기 조리법 — 전자레인지에 간편히 데워 샐러드나 도시락에 활용하기 용이함</t>
+          <t>간편한 조리 및 섭취 — 전자레인지 조리가 간편하며 한입 크기 볼 형태로 먹기 편함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>다소 늦은 배송 처리 — 제품 품질에 비해 배송 완료까지 시일이 조금 소요됨</t>
+          <t>지연되는 배송 — 배송 속도가 다소 느려 아쉬움</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3548,12 +3556,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>비리지 않은 맛있는 우유 맛 — 단백질 특유의 텁텁함이나 비린내 없이 모카/초코우유처럼 맛있음</t>
+          <t>비리지 않은 달달한 맛 — 단백질 특유의 텁텁함이 없고 진한 초코 음료 맛이 남</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>포만감 및 피부 부담 감소 — 운동 후 허기를 달래주며 분리유청 성분이라 피부 트러블 부담이 적음</t>
+          <t>운동 후 포만감 제공 — 운동 후 마시면 허기지지 않고 하루 섭취가 간편함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -3603,17 +3611,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>초고함량 아르기닌의 효과 — 6,200mg 고함량으로 운동 시 지구력 및 일상 활력이 빠르게 높아짐</t>
+          <t>초고함량으로 활력 증진 — 6,200mg 고함량 아르기닌으로 운동 시 체력과 컨디션 유지에 도움 됨</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>휴대하기 편한 스틱 포장 — 개별 스틱 형태라 외출 시 휴대하고 바로 먹기 편리함</t>
+          <t>휴대하기 편한 스틱형 — 1포씩 개별 포장되어 있어 들고 다니며 마시기 간편함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>고급 포장과 사은품 제공 — 쇼핑백과 추가 증정 포가 포함되어 남성 활력 선물용으로 뛰어남</t>
+          <t>선물에 적합한 블랙 패키지 — 고급스러운 블랙 포장과 전용 쇼핑백 증정으로 선물용에 적합함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3662,19 +3670,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>원활한 배변 및 가벼운 몸 — 꾸준 복용 시 변비 완화 및 몸이 가벼워지는 것을 체감함</t>
+          <t>소화 및 몸의 가벼움 — 지속 복용 시 몸이 가벼워지고 소화 및 배변 활동에 도움이 됨</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>정성스러운 포장과 좋은 맛 — 포장 상태가 깔끔하여 수령 시 기분이 좋고 맛도 편안함</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>알찬 저당 과자 증정 구성 — 저렴한 가격에 파로저당씬칩 등 사은품까지 함께 지급되어 만족스러움</t>
-        </is>
-      </c>
+          <t>합리적 가격과 증정품 — 저렴한 가격 구성에 스낵 등 추가 증정이 포함되어 만족스러움</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3721,22 +3725,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>확실한 다음 날 숙취 완화 — 음주 전후 섭취 시 아침의 묵직함과 숙취 증상이 확연히 줄어듦</t>
+          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 숙취가 현저히 덜함</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>휴대 편리한 액상 스틱 — 21ml 소용량 스틱이라 술자리에서 물 없이 간편히 복용함</t>
+          <t>고급스러운 기프트 박스 — 보라색 패키지와 쇼핑백 포장이 정성스럽고 고급스러움</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>선물에 적합한 보라색 패키지 — 고급스러운 보라색 상자와 리본 손잡이 포장으로 선물용에 어울림</t>
+          <t>물 없이 먹는 액상 스틱 — 개별 스틱 액상 제형으로 어디서나 물 없이 바로 섭취 가능함</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>약재/한약 맛에 대한 호불호 — 쌍화탕이나 한약 재료 향이 강해 쓴맛에 민감한 사람에겐 아쉬울 수 있음</t>
+          <t>한약 느낌의 호불호 맛 — 쌍화탕이나 한약재 같은 진한 맛이 나 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -4060,10 +4064,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16211</v>
+        <v>16213</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15526</v>
+        <v>15529</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3393</v>
@@ -4081,13 +4085,13 @@
         <v>808</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>778</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -4098,64 +4102,67 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>선물하기 좋은 포장과 구성 — 고급스러운 포장과 브랜드 인지도 덕에 선물용으로 만족도가 매우 높음
-빠른 피로 회복 효과 — 꾸준히 섭취 시 아침 피로가 풀리고 기력이 회복되는 느낌을 받음
-간편한 액상 정제 복용 — 액상과 정제를 함께 30초 만에 번거롭지 않게 섭취 가능함</t>
+          <t>우수한 섭취 및 휴대성 — 액상과 정제가 함께 있어 물 없이도 간편하게 섭취 가능하며 여행 시 휴대하기 용이함
+빠른 피로 회복 효과 — 복용 후 기력이 생기고 피로가 풀리며 정신이 드는 효과가 있음
+선물용으로 높은 만족도 — 패키지가 이쁘고 유명하여 선물용으로 높은 만족도를 얻음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>깔끔하고 예쁜 선물 패키지 — 패키지 박스가 깔끔하고 예뻐서 지인 선물용으로 매우 적합함
-간편한 올인원 영양 케어 — 다양한 비타민과 미네랄을 한 번에 간편하게 챙길 수 있음
-실용적이고 우수한 효과 — 실용적인 선물 구성이며 섭취 후 피로 개선 등 효과에 만족함</t>
+          <t>맛있는 음료 제형 — 주스처럼 거부감 없이 맛있게 즐길 수 있음
+피로 회복 및 활력 증진 — 섭취 후 피로 해소에 도움이 되고 개운함과 힘이 느껴짐
+간편한 섭취와 깔끔한 포장 — 포장이 깔끔하며 간편하게 챙겨 먹기 좋아 선물용으로 적합함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 포장이 고급스럽고 화려하여 주는 사람과 받는 사람 모두 만족함
-빠른 피로 회복 체감 — 피곤하고 힘들 때 섭취하면 빠르게 기운이 나는 효과를 체감함</t>
+          <t>체감 높은 피로 회복 — 힘들 때 반짝하는 효과를 주어 건강 관리에 도움 됨
+고급스러운 기프트 포장 — 포장이 고급스럽고 아름다워 선물하기에 마음에 듦</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>새콤달콤한 맛있는 구미 — 과일향이 풍부하고 새콤달콤하여 간식처럼 맛있게 먹을 수 있음
-거부감 없는 간편한 섭취 — 알약을 못 먹거나 목넘김이 어려운 사람도 매일 쉽게 챙겨 먹음</t>
+          <t>맛있는 과일 향과 식감 — 새콤달콤한 과일 향과 탱글하고 쫄깃한 식감으로 섭취가 즐거움
+편리한 구미 제형 — 씹어먹는 젤리 타입으로 물 없이 간식처럼 매일 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>알찬 수량 증정 구성 — 7입에 2입을 추가 증정하는 단독 구성이라 알차고 유용함
-피로 해소 및 기력 회복 — 지치고 피곤할 때 복용하면 아침 컨디션과 기력 회복에 도움 됨</t>
+          <t>깔끔하고 알찬 포장 구성 — 포장이 깔끔하고 증정 구성이 포함되어 생일 선물용으로 적합함
+아침 피로 개선 효과 — 복용 후 피로 해소 및 다음 날 아침 기력 회복에 도움을 줌
+간편한 올인원 제형 — 알약과 음료가 함께 있어 여러 영양제를 간편하게 하나로 챙길 수 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 명절 선물 포장 — 고급 박스와 종이가방이 포함되어 명절 선물용으로 격식 있음
-빠른 활력 충전 효과 — 피로감이 심할 때 섭취하면 빠르게 기운이 나고 활력이 생김</t>
+          <t>고급스러운 명절 포장 — 고급 박스와 종이가방 구성으로 명절 선물에 제격임
+활력 충전 효과 — 복용 시 피로가 가시고 기운을 차리는 데 도움이 됨</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>휴대와 복용의 편리함 — 외출 시 들고 다니며 간편하게 섭취하기 좋은 용기 형태임
-아침 활력 충전 효과 — 아침 복용 시 하루 활력이 생겨 직장 내 에너지 충전에 유용함</t>
+          <t>우수한 휴대성 및 편의성 — 간편하게 들고 다니며 섭취하기에 유용함
+빠른 배송과 가격 만족 — 배송이 빠르고 부담 없는 가격대에 구매가 가능함
+하루 활력 충전 — 아침 복용 시 일상과 사무실에서의 활력을 높여줌</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>상큼달콤한 맛과 섞는 재미 — 뚜껑을 눌러 분말을 섞는 재미가 있고 쓴 맛 없이 상큼하게 맛있음
-감기 예방 및 컨디션 회복 — 감기 기운이 있을 때 섭취하면 몸이 가벼워지고 기운이 남</t>
+          <t>상큼하고 달콤한 맛 — 쓴맛 없이 오렌지빛의 달달하고 상큼한 맛으로 맛있게 먹기 좋음
+재미있는 용기 메커니즘 — 뚜껑을 눌러 가루를 섞어 마시는 간편하고 독특한 재미가 있음
+고급스러운 선물 구성 — 포장과 봉투 구성이 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤형 제품 선택 — 남성용과 여성용이 구분되어 상황에 맞는 선물이 가능함
-쓴맛 없이 편한 복용 — 비타민 특유의 쓴맛이 없고 찐득하게 영양감이 느껴짐</t>
+          <t>성별 맞춤 선택 가능 — 남성과 여성에 맞춘 영양소 선택이 가능하여 유용함
+부담 없는 맛과 간편성 — 비타민 특유의 쓴맛이 없고 휴대하며 먹기 편함
+지속적인 피로 완화 — 꾸준히 복용 시 피로감이 줄고 활력 유지 효과를 봄</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>강력한 정신 확 깨는 효과 — 고함량 비타민 복용 시 나른한 컨디션이 개운해지고 정신이 듦
-선물용으로 훌륭한 브랜드 — 피로를 호소하는 지인에게 선물하기에 기분 좋은 아이템임</t>
+          <t>즉각적인 활력 제공 — 섭취 시 개운해지고 정신이 확 드는 느낌을 받음</t>
         </is>
       </c>
     </row>
@@ -4167,42 +4174,41 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>짧은 유통기한에 대한 아쉬움 — 수령 후 확인 시 유통기한이 10개월 미만으로 짧게 남아 아쉬움
-생각보다 작은 케이스 크기 — 손바닥 정도의 매우 작은 크기라 선물용 볼륨감으로 다소 미흡함</t>
+          <t>짧은 유통기한 배송 — 유통기한이 10개월 미만으로 남은 제품이 배송되어 아쉬움</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>발송자 정보 확인 불편 — 보낸 사람 정보 확인이 어렵고 카톡 고객문의 답변도 명확하지 않음</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>외관상 아쉬운 소포장 — 소포장 위주 구성이라 외관상 아주 풍성해 보이지는 않음</t>
-        </is>
-      </c>
+          <t>보낸 사람 확인 불가 — 선물 보낸 사람의 정보 확인이 불명확하고 문의 답변이 미흡함</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>하루 섭취량 제한의 아쉬움 — 젤리가 너무 맛있어 하루 2개 제한 이상으로 더 먹고 싶어 참기 힘듦</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>다소 높은 당 함유량 — 당 함유량이 4g 포함되어 있어 액상과당 섭취에 부담을 느낌</t>
+          <t>높은 당 함유량 — 당 함유량이 4g으로 다소 높게 느껴져 아쉬움</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>개봉 시 센 악력 필요 — 손 힘이 약한 사람은 뚜껑을 눌러서 열기가 다소 뻑뻑하고 힘듦</t>
+          <t>뚜껑 개봉의 어려움 — 손 힘이 약한 소비자의 경우 뚜껑을 열기 어려울 수 있음</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>삼키기 부담스러운 알약 크기 — 기존 제품에 비해 정제 알약 크기가 커서 삼키기가 다소 힘들음</t>
+          <t>큰 알약 크기 — 기존 제품 대비 알약 크기가 다소 커서 삼키기 힘듦</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>호불호 갈리는 강한 신맛 — 분말 특유의 신맛이 매우 강하여 섭취 시 강한 자극이 느껴짐
-캡슐 제형의 부재 — 가루를 직접 삼키기보다 캡슐 형태 제형을 선호하는 수요가 있음</t>
+          <t>강한 신맛으로 인한 거부감 — 분말 특유의 신맛이 매우 강해 섭취 시 맛에 대한 호불호가 갈림
+제형의 아쉬움 — 분말 형태로 인해 맛이 떨어져 캡슐 제형을 선호하는 의견이 있음</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4418,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -4464,17 +4470,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>아일로</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -4521,17 +4527,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인키위효소+고단백질바 증정</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -4609,16 +4615,16 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1685</v>
+        <v>60</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>1686</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>753</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>60</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>152</v>
@@ -4647,66 +4653,65 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 효소 맛과 풍미 — 효소 제품 중 최고 수준으로 맛있으며 골라 먹는 재미가 있음
-귀여운 굿즈 및 알찬 포장 — 콜라보 포토카드 퀄리티가 훌륭하고 패키지 포장이 예쁨</t>
+          <t>부담 없는 맛있는 풍미 — 효소 특유의 맛에 대한 부담 없이 맛있게 먹을 수 있음
+우수한 굿즈 기획 패키지 — 콜라보 굿즈 및 포토카드 포장 퀄리티가 우수함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>구수하고 거부감 없는 맛 — 구수한 고구마 맛이 나 부담 없이 온 가족이 먹기 좋음
-속이 편안해지는 소화 개선 — 식사나 밀가루 섭취 후 복용 시 속이 편해지고 소화에 도움 됨
-푸짐하고 알찬 증정 사은품 — 파로 곡물바와 차 등 다양한 사은품 구성이 함께 제공됨</t>
+          <t>부드럽고 촉촉한 식감 — 닭가슴살임에도 퍽퍽하지 않고 매우 부드러움
+다양한 맛과 가성비 — 다양한 종류 구성으로 질리지 않으며 세일 가격으로 구매하기 좋음</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>고급스럽고 예쁜 패키징 — 플리츠백과 오간자 포장 디자인이 화려하여 개봉 시 감동을 줌
-맛있고 섭취 편한 앰플 — 맛이 매우 우수하며 꾸준히 마실 시 피로감이 개선되는 느낌임</t>
+          <t>속 편한 소화 촉진 — 식후나 밀가루 섭취 후 복용 시 속이 편안해지고 소화에 도움을 줌
+구수한 고구마 맛 — 거부감 없는 구수한 고구마 맛으로 맛있게 섭취 가능함
+풍성한 사은품 증정 — 함께 증정되는 곡물바 및 사은품의 만족도가 높음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 식감 — 퍽퍽함과 잡내가 전혀 없고 극상의 부드러움을 느낄 수 있음
-다양한 맛과 가성비 할인 — 소스 및 제품 종류가 다채로워 질리지 않으며 할인가가 매우 저렴함</t>
+          <t>고급스러운 화려한 포장 — 개봉 시 기분이 좋아질 정도로 포장 패키지가 매우 예쁘고 고급스러움
+피로 회복 및 우수한 맛 — 맛이 좋고 섭취 시 피로감이 덜함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>우수한 포만감과 한 달 식단 — 한 개만 먹어도 포만감이 높아 다이어트 식단으로 매우 든든함
-실용적인 보냉백 사은품 — 증정품으로 오는 보냉 도시락 가방이 예쁘고 들고 다니기 좋음</t>
+          <t>높은 포만감과 맛 — 한 개만 먹어도 속이 든든하며 다양한 소스 맛이 훌륭함
+알찬 식단 패키지 — 30팩의 풍성한 수량으로 한 달 식단 관리에 유용함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>쫄깃하고 부드러운 식감 — 닭가슴살과 볼 제형 모두 촉촉하고 부드러워 먹기 수월함
-간 편한 데우기 조리법 — 전자레인지에 간편히 데워 샐러드나 도시락에 활용하기 용이함</t>
+          <t>부드럽고 쫄깃한 맛 — 퍽퍽하지 않고 촉촉하여 맛있게 단백질 충전이 가능함
+간편한 조리 및 섭취 — 전자레인지 조리가 간편하며 한입 크기 볼 형태로 먹기 편함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>비리지 않은 맛있는 우유 맛 — 단백질 특유의 텁텁함이나 비린내 없이 모카/초코우유처럼 맛있음
-포만감 및 피부 부담 감소 — 운동 후 허기를 달래주며 분리유청 성분이라 피부 트러블 부담이 적음</t>
+          <t>비리지 않은 달달한 맛 — 단백질 특유의 텁텁함이 없고 진한 초코 음료 맛이 남
+운동 후 포만감 제공 — 운동 후 마시면 허기지지 않고 하루 섭취가 간편함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>초고함량 아르기닌의 효과 — 6,200mg 고함량으로 운동 시 지구력 및 일상 활력이 빠르게 높아짐
-휴대하기 편한 스틱 포장 — 개별 스틱 형태라 외출 시 휴대하고 바로 먹기 편리함
-고급 포장과 사은품 제공 — 쇼핑백과 추가 증정 포가 포함되어 남성 활력 선물용으로 뛰어남</t>
+          <t>초고함량으로 활력 증진 — 6,200mg 고함량 아르기닌으로 운동 시 체력과 컨디션 유지에 도움 됨
+휴대하기 편한 스틱형 — 1포씩 개별 포장되어 있어 들고 다니며 마시기 간편함
+선물에 적합한 블랙 패키지 — 고급스러운 블랙 포장과 전용 쇼핑백 증정으로 선물용에 적합함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>원활한 배변 및 가벼운 몸 — 꾸준 복용 시 변비 완화 및 몸이 가벼워지는 것을 체감함
-정성스러운 포장과 좋은 맛 — 포장 상태가 깔끔하여 수령 시 기분이 좋고 맛도 편안함
-알찬 저당 과자 증정 구성 — 저렴한 가격에 파로저당씬칩 등 사은품까지 함께 지급되어 만족스러움</t>
+          <t>소화 및 몸의 가벼움 — 지속 복용 시 몸이 가벼워지고 소화 및 배변 활동에 도움이 됨
+합리적 가격과 증정품 — 저렴한 가격 구성에 스낵 등 추가 증정이 포함되어 만족스러움</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>확실한 다음 날 숙취 완화 — 음주 전후 섭취 시 아침의 묵직함과 숙취 증상이 확연히 줄어듦
-휴대 편리한 액상 스틱 — 21ml 소용량 스틱이라 술자리에서 물 없이 간편히 복용함
-선물에 적합한 보라색 패키지 — 고급스러운 보라색 상자와 리본 손잡이 포장으로 선물용에 어울림</t>
+          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 숙취가 현저히 덜함
+고급스러운 기프트 박스 — 보라색 패키지와 쇼핑백 포장이 정성스럽고 고급스러움
+물 없이 먹는 액상 스틱 — 개별 스틱 액상 제형으로 어디서나 물 없이 바로 섭취 가능함</t>
         </is>
       </c>
     </row>
@@ -4717,26 +4722,26 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>부담스러운 높은 가격대 — 제품 단가가 높은 편이라 주로 세일 기간이나 선물용으로만 구매함</t>
-        </is>
-      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>특정 구성의 부재 — 선호하는 파우치형 그릴 제품이 구성에 포함되어 있지 않아 아쉬움</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>선호 품목 구성 제외 아쉬움 — 개인적으로 선호하는 파우치형 그릴 제품이 빠져있어 아쉬움</t>
+          <t>부담스러운 가격 — 가격대가 높아 할인 시에만 구매하게 됨</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>제품 터짐 및 소스 누출 — 포장이 헐렁하거나 봉지가 터져서 주변에 소스가 묻어 배송됨
-구성품 오배송 발생 — 안내된 옵션과 다르게 제품이 누락되거나 중복되어 잘못 전달됨</t>
+          <t>구성품 오배송 — 주문한 구성과 다르게 제품이 중복되거나 누락되어 배송됨
+포장 파손 및 진공 불량 — 배송 과정에서 제품이 터져 소스가 묻거나 진공 포장이 헐렁함</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>다소 늦은 배송 처리 — 제품 품질에 비해 배송 완료까지 시일이 조금 소요됨</t>
+          <t>지연되는 배송 — 배송 속도가 다소 느려 아쉬움</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
@@ -4744,7 +4749,7 @@
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>약재/한약 맛에 대한 호불호 — 쌍화탕이나 한약 재료 향이 강해 쓴맛에 민감한 사람에겐 아쉬울 수 있음</t>
+          <t>한약 느낌의 호불호 맛 — 쌍화탕이나 한약재 같은 진한 맛이 나 호불호가 갈릴 수 있음</t>
         </is>
       </c>
     </row>
@@ -4761,17 +4766,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
+          <t>33,900원</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>42,900원</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>65,900원</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>33,900원</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -4991,7 +4996,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4999,58 +5004,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762097&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250807/jJGIxkBNqg0FzVjNiyoV901762097_00_01jJGIxkBNqg0FzVjNiyoV.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260930/WeHdQCGpAxVMhBizdMLr030086178_00_00WeHdQCGpAxVMhBizdMLr.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>1116</v>
+        <v>896</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>뛰어난 가성비의 홍삼정 — 저렴한 가격으로 부담 없이 꾸준히 복용하기 좋은 가성비 제품임</t>
+          <t>상큼하고 풍부한 맛 — 상큼하고 맛있어서 간식용으로 먹기 좋음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>휴대 편의성과 과하지 않은 단맛 — 가볍게 들고 다니며 먹기 쉽고 달지 않아 질리지 않음</t>
+          <t>저렴한 가성비 — 가격이 저렴하여 부담 없이 재구매하기 좋음</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>재구매 시 자주 발생하는 품절 — 인기가 많아 재구매하려 할 때 품절되어 재입고를 기다려야 함</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5058,49 +5059,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953529&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/vXg1N5D0xbSNweDPvvl2994953529_00_00vXg1N5D0xbSNweDPvvl2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>393</v>
+        <v>514</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>달지 않고 깔끔한 석류 맛 — 달지 않아서 물에 타 마시기 좋고 석류식초처럼 깔끔한 맛임</t>
+          <t>확실한 배변 반응 — 섭취 후 물을 충분히 마시면 쾌변 효과가 나타남</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>빠른 배송과 휴대 편의성 — 배송이 신속하며 포장이 낱개로 되어 있어 휴대가 용이함</t>
+          <t>부담 없는 적당한 단맛 — 많이 달지 않아 마시기 편함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>사용자에 따른 맛 호불호 — 개인 취향에 따라 석류 맛이나 품질 면에서 만족도가 떨어질 수 있음</t>
+          <t>심한 변비에는 미미한 효과 — 일반 편의점 제품보다 강도가 낮고 심한 변비에는 체감이 약함</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -5117,54 +5118,62 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>2512</v>
+        <v>154</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 철분제 — 가격이 착해 매일매일 부담 없이 챙겨 먹기 적합함</t>
+          <t>부담 없는 한약 풍미 — 쓴맛이 너무 강하지 않아 복용에 어려움이 없음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>어지러움 케어 및 건강 체감 — 꾸준한 복용으로 몸이 한결 건강해지는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>기력 및 근력 증진 — 기력이 떨어질 때 섭취 후 근력 및 컨디션 상승 효과를 염두에 둠</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>부담 없는 가성비 — 저렴한 가격으로 침향환을 접할 수 있음</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>특유의 쓴맛 존재 — 몸에는 좋으나 제품 특성상 약간의 쓴맛이 있음</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5172,58 +5181,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2784</v>
+        <v>821</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>피로 및 생리증후군 완화 — 피곤하거나 생리 전 복용 시 컨디션 유지에 도움을 받음</t>
+          <t>압도적인 다이소 가성비 — 타 채널 대비 매우 저렴한 가격에 구매할 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>속 부대낌 없는 편안함 — 비타민C 특유의 소화 불량이나 속 쓰림 증상이 없음</t>
+          <t>운동 전 간편한 섭취 — 운동 갈 때 가볍게 하나씩 챙겨 마시기 편리함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>약간 크게 느껴지는 알약 — 영양 보충엔 좋으나 정제 알약 크기가 다소 크게 느껴짐</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5231,7 +5236,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 콜라겐 60정 30일분</t>
+          <t>대웅제약 멀티비타민미네랄 6정 6일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5241,44 +5246,40 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000138&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000283&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0buLkRj5uSU3KVXDKEhY600000138_00_000buLkRj5uSU3KVXDKEhY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/zIbSOpTi3yHSeYULrLdY600000283_00_01zIbSOpTi3yHSeYULrLdY.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1346</v>
+        <v>273</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>저렴한 가격과 적절한 크기 — 가격 부담이 없고 목넘김이 무난하여 매일 먹기 좋음</t>
+          <t>질리지 않는 소용량 구성 — 대용량 포장에 질리는 소비자를 위한 부담 없는 소포장 구성</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>눈에 띄는 효과 체감 부족 — 단기 복용 시 눈으로 보이는 직접적인 효과는 확인하기 어려움</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5286,12 +5287,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>동국제약 이너케어＆유산균 30캡슐</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5301,28 +5302,28 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2853</v>
+        <v>6550</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>장 편안함 및 배변 도움 — 복용 후 장이 편안해지고 대변이 잘 나오는 효과를 체감함</t>
+          <t>꾸준한 구매가 가능한 가성비 — 가격 부담이 없어 매일 챙겨 먹기 좋고 재구매율이 높음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>삼키기 쉬운 작은 캡슐 — 알약 크기가 작아 목넘김이 편하고 가격 대비 성능이 훌륭함</t>
+          <t>쉬운 오프라인 접근성 — 필요할 때 쉽게 구매가 가능하여 유용함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -5333,7 +5334,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5341,12 +5342,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5356,39 +5357,47 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602124&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251216/mSQXyRQCV8ORV8edPm4n613602124_00_01mSQXyRQCV8ORV8edPm4n.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1226</v>
+        <v>1903</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>관절 및 무릎 통증 완화 — 꾸준히 복용 시 무릎 상태가 확실히 편해지는 것을 경험함</t>
+          <t>뛰어난 피로 회복 체감 — 몸이 지치거나 에너지가 부족할 때 빠른 피로 회복을 도움</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>믿을 수 있는 제약사 브랜드 — 대웅제약 브랜드라 신뢰가 가며 부모님께 주기 적절함</t>
+          <t>놀라운 저렴함 — 이뮨 비타민을 매우 저렴한 가격에 살 수 있음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>간혹 생기는 소화 불편 — 섭취 후 가끔 소화가 잘되지 않을 때가 있음</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>잦은 일시 품절 — 인기가 많아 자주 품절되어 재입고를 기다려야 함</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5396,7 +5405,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 숙취해소 노니샷 5포 5회분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5406,37 +5415,41 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000151&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250507/h6NVof0E9taNldehzI8v600000151_00_00h6NVof0E9taNldehzI8v.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>643</v>
+        <v>6564</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>부담 없는 가격과 맛있는 제형 — 저렴한 가격에 맛도 좋아 음주 전 간편히 챙겨 마시기 편함</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>명확하지 않은 숙취 효과 — 맛은 좋으나 실제 숙취 해소에 미치는 효과 체감은 명확지 않음</t>
-        </is>
-      </c>
+          <t>근육 완화 및 쾌변 도움 — 어깨 뭉침 완화나 배변 활동 개선에 실질적인 도움을 받음</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>군더더기 없는 단일 성분 — 불필요한 성분이 섞이지 않아 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>쟁여두기 좋은 가성비 — 가격이 저렴해 집에 쟁여두고 꾸준히 복용하기 좋음</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -5451,12 +5464,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5466,34 +5479,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000130&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306284&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0tJFRHjUfKCxN5mKhDV0600000130_00_000tJFRHjUfKCxN5mKhDV0.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260805/e483TrUWUwCko9CBv1Da032306284_00_00e483TrUWUwCko9CBv1Da.png</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1541</v>
+        <v>135</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>한 달 단위의 깔끔한 관리 — 30일분 포장으로 매일 한 정씩 챙겨 먹기 용이함</t>
+          <t>수면 질 향상 도움 — 섭취 후 안 먹었을 때보다 잠이 잘 옴</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>저렴하고 자극 없는 복용 — 가격 부담이 적고 자극 없이 피부 관리를 이어가기 적합함</t>
+          <t>소소한 뜯는 재미 — 약 포장을 하나씩 부수어 꺼내는 재미가 있음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>단기 복용 시 미미한 효과 — 하루 한 정 단기 복용으로는 피부 개선 효과를 즉각 느끼기 어려움</t>
+          <t>다이어트 효과 체감 불확실 — 체중 감량 관련 효능은 확실하게 느끼기 어려움</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -5502,7 +5515,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5510,47 +5523,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
+          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982831&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=025575127&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/lX1R9GhsEUzz72XUg7VZ611982831_00_00lX1R9GhsEUzz72XUg7VZ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/VsX5iaJon2xHHTs8AQHv025575127_00_01VsX5iaJon2xHHTs8AQHv.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>1501</v>
+        <v>924</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>먹기 편한 미니 캡슐 — 캡슐 크기가 작아 속 부담 없이 쉽게 삼킬 수 있음</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>착한 가격의 루테인 관리 — 저렴한 가격으로 눈 건강 성분을 매일 보충하기 좋음</t>
-        </is>
-      </c>
+          <t>식후 소화 지원 — 식사 후 소화가 잘되도록 돕는 효소 역할을 함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>붓기 개선 미미 — 붓기 완화와 관련된 체감 효과는 명확히 알기 어려움</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5665,12 +5678,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -5680,37 +5693,37 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
         </is>
       </c>
     </row>
@@ -5722,52 +5735,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>홀베리</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>휴럼</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>자연관</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>셀트리온</t>
         </is>
       </c>
     </row>
@@ -5779,52 +5792,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 콜라겐 60정 30일분</t>
+          <t>대웅제약 멀티비타민미네랄 6정 6일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 이너케어＆유산균 30캡슐</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 숙취해소 노니샷 5포 5회분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
+          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
         </is>
       </c>
     </row>
@@ -5835,13 +5848,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>4.7</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.8</v>
@@ -5856,13 +5869,13 @@
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>4.7</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5872,37 +5885,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1116</v>
+        <v>896</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>393</v>
+        <v>514</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2512</v>
+        <v>154</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2784</v>
+        <v>821</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1346</v>
+        <v>273</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2853</v>
+        <v>6550</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1226</v>
+        <v>1903</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>643</v>
+        <v>6564</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1541</v>
+        <v>135</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1501</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5910,103 +5923,102 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비의 홍삼정 — 저렴한 가격으로 부담 없이 꾸준히 복용하기 좋은 가성비 제품임
-휴대 편의성과 과하지 않은 단맛 — 가볍게 들고 다니며 먹기 쉽고 달지 않아 질리지 않음</t>
+          <t>상큼하고 풍부한 맛 — 상큼하고 맛있어서 간식용으로 먹기 좋음
+저렴한 가성비 — 가격이 저렴하여 부담 없이 재구매하기 좋음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>달지 않고 깔끔한 석류 맛 — 달지 않아서 물에 타 마시기 좋고 석류식초처럼 깔끔한 맛임
-빠른 배송과 휴대 편의성 — 배송이 신속하며 포장이 낱개로 되어 있어 휴대가 용이함</t>
+          <t>확실한 배변 반응 — 섭취 후 물을 충분히 마시면 쾌변 효과가 나타남
+부담 없는 적당한 단맛 — 많이 달지 않아 마시기 편함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 철분제 — 가격이 착해 매일매일 부담 없이 챙겨 먹기 적합함
-어지러움 케어 및 건강 체감 — 꾸준한 복용으로 몸이 한결 건강해지는 느낌을 받음</t>
+          <t>부담 없는 한약 풍미 — 쓴맛이 너무 강하지 않아 복용에 어려움이 없음
+기력 및 근력 증진 — 기력이 떨어질 때 섭취 후 근력 및 컨디션 상승 효과를 염두에 둠
+부담 없는 가성비 — 저렴한 가격으로 침향환을 접할 수 있음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>피로 및 생리증후군 완화 — 피곤하거나 생리 전 복용 시 컨디션 유지에 도움을 받음
-속 부대낌 없는 편안함 — 비타민C 특유의 소화 불량이나 속 쓰림 증상이 없음</t>
+          <t>압도적인 다이소 가성비 — 타 채널 대비 매우 저렴한 가격에 구매할 수 있음
+운동 전 간편한 섭취 — 운동 갈 때 가볍게 하나씩 챙겨 마시기 편리함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 가격과 적절한 크기 — 가격 부담이 없고 목넘김이 무난하여 매일 먹기 좋음</t>
+          <t>질리지 않는 소용량 구성 — 대용량 포장에 질리는 소비자를 위한 부담 없는 소포장 구성</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>장 편안함 및 배변 도움 — 복용 후 장이 편안해지고 대변이 잘 나오는 효과를 체감함
-삼키기 쉬운 작은 캡슐 — 알약 크기가 작아 목넘김이 편하고 가격 대비 성능이 훌륭함</t>
+          <t>꾸준한 구매가 가능한 가성비 — 가격 부담이 없어 매일 챙겨 먹기 좋고 재구매율이 높음
+쉬운 오프라인 접근성 — 필요할 때 쉽게 구매가 가능하여 유용함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>관절 및 무릎 통증 완화 — 꾸준히 복용 시 무릎 상태가 확실히 편해지는 것을 경험함
-믿을 수 있는 제약사 브랜드 — 대웅제약 브랜드라 신뢰가 가며 부모님께 주기 적절함</t>
+          <t>뛰어난 피로 회복 체감 — 몸이 지치거나 에너지가 부족할 때 빠른 피로 회복을 도움
+놀라운 저렴함 — 이뮨 비타민을 매우 저렴한 가격에 살 수 있음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 가격과 맛있는 제형 — 저렴한 가격에 맛도 좋아 음주 전 간편히 챙겨 마시기 편함</t>
+          <t>근육 완화 및 쾌변 도움 — 어깨 뭉침 완화나 배변 활동 개선에 실질적인 도움을 받음
+군더더기 없는 단일 성분 — 불필요한 성분이 섞이지 않아 만족도가 높음
+쟁여두기 좋은 가성비 — 가격이 저렴해 집에 쟁여두고 꾸준히 복용하기 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>한 달 단위의 깔끔한 관리 — 30일분 포장으로 매일 한 정씩 챙겨 먹기 용이함
-저렴하고 자극 없는 복용 — 가격 부담이 적고 자극 없이 피부 관리를 이어가기 적합함</t>
+          <t>수면 질 향상 도움 — 섭취 후 안 먹었을 때보다 잠이 잘 옴
+소소한 뜯는 재미 — 약 포장을 하나씩 부수어 꺼내는 재미가 있음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>먹기 편한 미니 캡슐 — 캡슐 크기가 작아 속 부담 없이 쉽게 삼킬 수 있음
-착한 가격의 루테인 관리 — 저렴한 가격으로 눈 건강 성분을 매일 보충하기 좋음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>식후 소화 지원 — 식사 후 소화가 잘되도록 돕는 효소 역할을 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>재구매 시 자주 발생하는 품절 — 인기가 많아 재구매하려 할 때 품절되어 재입고를 기다려야 함</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>사용자에 따른 맛 호불호 — 개인 취향에 따라 석류 맛이나 품질 면에서 만족도가 떨어질 수 있음</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>약간 크게 느껴지는 알약 — 영양 보충엔 좋으나 정제 알약 크기가 다소 크게 느껴짐</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>눈에 띄는 효과 체감 부족 — 단기 복용 시 눈으로 보이는 직접적인 효과는 확인하기 어려움</t>
-        </is>
-      </c>
+          <t>심한 변비에는 미미한 효과 — 일반 편의점 제품보다 강도가 낮고 심한 변비에는 체감이 약함</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>특유의 쓴맛 존재 — 몸에는 좋으나 제품 특성상 약간의 쓴맛이 있음</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>명확하지 않은 숙취 효과 — 맛은 좋으나 실제 숙취 해소에 미치는 효과 체감은 명확지 않음</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>간혹 생기는 소화 불편 — 섭취 후 가끔 소화가 잘되지 않을 때가 있음
+잦은 일시 품절 — 인기가 많아 자주 품절되어 재입고를 기다려야 함</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>단기 복용 시 미미한 효과 — 하루 한 정 단기 복용으로는 피부 개선 효과를 즉각 느끼기 어려움</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>다이어트 효과 체감 불확실 — 체중 감량 관련 효능은 확실하게 느끼기 어려움</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>붓기 개선 미미 — 붓기 완화와 관련된 체감 효과는 명확히 알기 어려움</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6016,52 +6028,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>1,500원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6252,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6248,27 +6260,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[수면기능성] 세렌 굿슬립 아쉬아간다 앤 마그네슘 15포 (15일분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>세렌</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>38,500원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000251562&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025156213ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6283,7 +6295,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6291,33 +6303,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>553</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>체지방과 장 건강 이중 케어 — 장 건강 개선과 체지방 감소를 동시에 관리할 수 있어 다이어트에 도움 됨</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>상큼한 요거트 맛 — 거부감 없는 상큼한 요거트 맛으로 1일 1포 챙기기 용이함</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -6326,7 +6350,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6334,32 +6358,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246271&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627107ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24958</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>아침 공복에 간편한 케어 — 아침 빈속에 1캡슐로 장 건강을 챙길 수 있음</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -6377,33 +6409,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>17141</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>야식 및 촬영 전 붓기 완화 — 야식 후나 중요한 날 전 붓기를 정돈해 줌</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>섭취 편한 미니환 제형 — 환 크기가 미니 사이즈라 물과 함께 목넘김이 쉬움</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -6420,33 +6464,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8360</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>여성 맞춤 영양 설계 — 질 건강과 필수 영양을 아침 루틴으로 함께 챙김</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>귀여운 증정 기획 — 키링 등 만족스러운 콜라보 기획 구성품이 제공됨</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -6455,7 +6511,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6463,33 +6519,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364590ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31431</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>과식 후 뱃살 및 배변 케어 — 과식 후 더부룩한 뱃살 완화와 배변 활동 촉진 효과가 뛰어남</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>새콤달콤한 젤리 식감 — 탱글한 젤리 식감에 과일 맛이 더해져 간식 대용으로 즐기기 좋음</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6498,7 +6566,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6506,43 +6574,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993407ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>24950</v>
+        <v>2347</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>간편한 1일 1캡슐 루틴 — 아침 공복에 물과 한 알로 장 건강과 면역을 챙길 수 있음</t>
+          <t>변비 해결 및 배변 도움 — 만성 변비 해소와 아윗배 케어에 효과적임</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>알찬 더블 기획 구성 — 60캡슐 더블 기획으로 두 달 동안 넉넉하게 복용 가능함</t>
+          <t>씹히는 치아씨드 식감 — 젤리 속 치아씨드가 씹히는 식감이 좋아 맛있게 먹기 편함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -6553,7 +6621,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6561,33 +6629,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>에버콜라겐 인앤업비오틴 셀 56정 (28일분)</t>
+          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>에버콜라겐</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23,900원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000186592&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018659252ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807374ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6528</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3중 식후 멀티 케어 — 카테킨과 비타민 C, D를 통해 체지방과 항산화를 식후에 케어함</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>소장 가치 높은 캐릭터 키링 — 시나모롤 틴케이스 키링 증정 구성으로 만족도가 극대화됨</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -6596,7 +6676,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6604,39 +6684,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[국민영양] 여에스더 초임계 알티지 오메가3 30캡슐 3박스/5박스 (3개월분/5개월분)</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>에스더포뮬러</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26,700원</t>
+          <t>24,500원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=B000000228337&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/B00000022833705ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>1925</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>19194</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>자극적인 안주 및 붓기 관리 — 맵단짠 음식이나 야식 섭취 후 라인 관리에 유용함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>물 없이 마시는 포도 맛 액상 — 휴대가 용이한 포 형태의 상큼한 포도 맛으로 간편 섭취 가능함</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>미세하게 남아있는 한약 맛 — 상큼한 포도 맛 뒤에 약간의 한약 맛이 은은하게 섞여 느껴짐</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -6651,47 +6743,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>미에로화이바</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10,900원</t>
+          <t>9,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000268343&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587421ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>맛있는 레몬라임 구미 — 물 없이 씹어 먹는 상큼한 맛으로 피로를 줄이는 간식 같음</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>합리적인 세일 구매 기회 — 올영세일 프로모션 적용 시 가격대가 합리적임</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026834303ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>32</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>섭취 후 양치 필요성 — 젤리 제형 특성상 밤이나 게으른 날 섭취 후 양치를 다시 해야 함</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -6806,17 +6890,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -6831,22 +6915,22 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -6863,52 +6947,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>세렌</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>글로우뮤즈</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>에버콜라겐</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>에스더포뮬러</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>미에로화이바</t>
         </is>
       </c>
     </row>
@@ -6920,52 +7004,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[수면기능성] 세렌 굿슬립 아쉬아간다 앤 마그네슘 15포 (15일분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>에버콜라겐 인앤업비오틴 셀 56정 (28일분)</t>
+          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[국민영양] 여에스더 초임계 알티지 오메가3 30캡슐 3박스/5박스 (3개월분/5개월분)</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
         </is>
       </c>
     </row>
@@ -6976,19 +7060,33 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="I6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="K6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -6997,19 +7095,33 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="n">
+        <v>553</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>24958</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>17141</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>8360</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>31431</v>
+      </c>
       <c r="I7" s="3" t="n">
-        <v>24950</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
+        <v>2347</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>6528</v>
+      </c>
       <c r="K7" s="3" t="n">
-        <v>1925</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+        <v>19194</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
@@ -7018,25 +7130,54 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>체지방과 장 건강 이중 케어 — 장 건강 개선과 체지방 감소를 동시에 관리할 수 있어 다이어트에 도움 됨
+상큼한 요거트 맛 — 거부감 없는 상큼한 요거트 맛으로 1일 1포 챙기기 용이함</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>아침 공복에 간편한 케어 — 아침 빈속에 1캡슐로 장 건강을 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>야식 및 촬영 전 붓기 완화 — 야식 후나 중요한 날 전 붓기를 정돈해 줌
+섭취 편한 미니환 제형 — 환 크기가 미니 사이즈라 물과 함께 목넘김이 쉬움</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>여성 맞춤 영양 설계 — 질 건강과 필수 영양을 아침 루틴으로 함께 챙김
+귀여운 증정 기획 — 키링 등 만족스러운 콜라보 기획 구성품이 제공됨</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>과식 후 뱃살 및 배변 케어 — 과식 후 더부룩한 뱃살 완화와 배변 활동 촉진 효과가 뛰어남
+새콤달콤한 젤리 식감 — 탱글한 젤리 식감에 과일 맛이 더해져 간식 대용으로 즐기기 좋음</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>간편한 1일 1캡슐 루틴 — 아침 공복에 물과 한 알로 장 건강과 면역을 챙길 수 있음
-알찬 더블 기획 구성 — 60캡슐 더블 기획으로 두 달 동안 넉넉하게 복용 가능함</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 레몬라임 구미 — 물 없이 씹어 먹는 상큼한 맛으로 피로를 줄이는 간식 같음
-합리적인 세일 구매 기회 — 올영세일 프로모션 적용 시 가격대가 합리적임</t>
-        </is>
-      </c>
+          <t>변비 해결 및 배변 도움 — 만성 변비 해소와 아윗배 케어에 효과적임
+씹히는 치아씨드 식감 — 젤리 속 치아씨드가 씹히는 식감이 좋아 맛있게 먹기 편함</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>3중 식후 멀티 케어 — 카테킨과 비타민 C, D를 통해 체지방과 항산화를 식후에 케어함
+소장 가치 높은 캐릭터 키링 — 시나모롤 틴케이스 키링 증정 구성으로 만족도가 극대화됨</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>자극적인 안주 및 붓기 관리 — 맵단짠 음식이나 야식 섭취 후 라인 관리에 유용함
+물 없이 마시는 포도 맛 액상 — 휴대가 용이한 포 형태의 상큼한 포도 맛으로 간편 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7052,12 +7193,12 @@
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>섭취 후 양치 필요성 — 젤리 제형 특성상 밤이나 게으른 날 섭취 후 양치를 다시 해야 함</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>미세하게 남아있는 한약 맛 — 상큼한 포도 맛 뒤에 약간의 한약 맛이 은은하게 섞여 느껴짐</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -7067,52 +7208,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>38,500원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>35,800원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>26,800원</t>
-        </is>
-      </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>23,900원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26,700원</t>
+          <t>24,500원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>10,900원</t>
+          <t>9,900원</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7242,98 +7383,98 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
         <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D4" t="n">
         <v>7</v>
       </c>
-      <c r="C4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
       <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -7342,23 +7483,23 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -7374,16 +7515,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7392,23 +7533,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
         <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
